--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-03_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-03_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -1656,37 +1656,37 @@
         <v>56</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>73.2</v>
+        <v>100</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>131</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="23" t="n">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="M5" s="23" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1699,19 +1699,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>3</v>
@@ -1742,19 +1742,19 @@
         <v>2</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>4</v>
@@ -1785,37 +1785,37 @@
         <v>8</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>68.8</v>
+        <v>100</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="M8" s="23" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1828,37 +1828,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M9" s="23" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1871,19 +1871,19 @@
         <v>2</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>5</v>
@@ -1914,19 +1914,19 @@
         <v>2</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>6</v>
@@ -1957,37 +1957,37 @@
         <v>2</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="23" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M12" s="23" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2000,19 +2000,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>2</v>
@@ -2043,37 +2043,37 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="23" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="M14" s="23" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -2086,19 +2086,19 @@
         <v>1</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>3</v>
@@ -2129,19 +2129,19 @@
         <v>3</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="23" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>9</v>
@@ -2172,19 +2172,19 @@
         <v>4</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>13</v>
@@ -2215,19 +2215,19 @@
         <v>2</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>4</v>
@@ -2258,19 +2258,19 @@
         <v>2</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>5</v>
@@ -2301,19 +2301,19 @@
         <v>1</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>1</v>
@@ -2387,19 +2387,19 @@
         <v>1</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>1</v>
@@ -2516,37 +2516,37 @@
         <v>1</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="23" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="M25" s="23" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -2559,19 +2559,19 @@
         <v>2</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>3</v>
@@ -2903,37 +2903,37 @@
         <v>1</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Planned extension – Adopt BDOI's KPIs and filters in the FRS text; add the filters and PDF/CSV export to the home page; keep our service-level colours.</t>
+          <t>BDOI's text is met: Product Maintenance Dashboard with BDOI's indicators (incoming, in progress, for approval, expiring, issued, deactivation), date, officer, line and packaged filters, drill-down list and PDF, Excel and CSV export (TC-FRPM.001.01 cases).</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Decide where non-package requests are documented and placed in the menu (sheet 8, C01).</t>
+          <t>BDOI's text is met: Quotation requests of non-package products listed and opened from the Product Maintenance landing page, with the requests of the package path (TC-FRPM.002.01 cases).</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Adopt BDOI wording – Describe the landing page in BDOI's terms with our screens behind each tab; add Account Officer and Submission Date to the Package Requests list (small platform change).</t>
+          <t>BDOI's text is met: Landing page tabs Product Matrix, Quotation Request List and Package Request List with Account Officer and Submission Date (TC-FRPM.002.02 cases).</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Planned extension – Add BDOI's columns and the export to the Products list.</t>
+          <t>BDOI's text is met: Product Matrix with Active, Expiring and Expired Products tabs, BDOI's columns, search, sort and export (TC-FRPM.003.01 cases).</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Decide direct maintenance vs request route, the incentive flag and named approvers (sheet 8, C09, C19, C08); add Annex A fields to the package version (platform change).</t>
+          <t>BDOI's text is met: Direct add and update of Product Matrix records with package description, incentive flag and named approver; the request route stays available by setting (TC-FRPM.003.02 cases).</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Choose the deactivation route (sheet 8, C10).</t>
+          <t>BDOI's text is met: Deactivate Package with effective date, reason, remarks and approver; the retirement request route stays available by setting (TC-FRPM.003.04 cases).</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Adopt BDOI wording – Describe the list as a filtered view of Package Requests; add the effective date if the deactivation route of C10 is adopted.</t>
+          <t>BDOI's text is met: Deactivation Requests list with request number, package, effective date, status and approver (TC-FRPM.003.06 cases).</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Follows C10; platform change if the effective-dated deactivation is adopted.; some acceptance criteria partly available</t>
+          <t>BDOI's text is met: Approve, reject with remarks, cancel and reassign of deactivation requests; the package expires on the effective date (TC-FRPM.003.07 cases).</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Planned extension – Set the notice period to 90 days (configuration); add the anniversary alert (platform change); confirm recipients (sheet 8, C02).; some acceptance criteria partly available</t>
+          <t>BDOI's text is met: Expiry notice at 90 days and the package anniversary notice to TSU, MBS by setting (TC-FRPM.004.01 cases).</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Scope and status names (sheet 8, C01, C16).</t>
+          <t>BDOI's text is met: Quotation Request List with BDOI's status names, search, filters and aging (TC-FRPM.005.01 cases).</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Planned extension – File naming per BDOI's convention (C23); keep sending from the system (C12).</t>
+          <t>BDOI's text is met: Quotation slip sent to each insurer as QS_&lt;Reference&gt;_&lt;Insurer&gt;_MMDDYYYY.pdf (TC-FRPM.006.01 cases).</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Multiple options per insurer and the response list (C14, C15).</t>
+          <t>BDOI's text is met: Comparative table with the QS value column, several quotation options per insurer and the responses Approved, Not Covered and Others (TC-FRPM.006.02 cases).</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Scope (quotation requests, package requests or accounts), schedule and columns (C03); platform change for the weekly run and repository.; some acceptance criteria partly available</t>
+          <t>BDOI's text is met: Consolidated Placement Update Report every Thursday at 08:00 (configurable) with BDOI's twelve columns, PlacementUpdate_MMDDYYYY.xlsx, repository with preview and download (TC-FRPM.007.01 cases).</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Who selects the insurers and when (C18).</t>
+          <t>BDOI's text is met: The requestor selects the insurers that gave terms and proceeds to the proposal; the request shows Terms Agreed and TSU is told (TC-FRPM.008.01 cases).</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Planned extension – Add the Final Terms column if BDOI keeps the proposal step (C18).; some acceptance criteria partly available</t>
+          <t>BDOI's text is met: Final Terms for Proposal column filled from the selected insurer, editable, every change kept in its history (TC-FRPM.009.01 cases).</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Planned extension – Several insurers per generation and the file naming.</t>
+          <t>BDOI's text is met: Generate Proposal: one proposal slip per selected insurer named ProposalSlip_&lt;Reference&gt;_&lt;Insurer&gt;_&lt;Version&gt;_MMDDYYYY.pdf, approved by a second TSU officer (TC-FRPM.009.02 cases).</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Planned extension – Client return for revision, if BDOI keeps it.</t>
+          <t>BDOI's text is met: Record Client Response: Accepted, Rejected or Return for Revision with remarks, response date and notices (TC-FRPM.010.01 cases).</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Approval chain and source routing (C05, C07); add Annex E fields to the form (platform change).</t>
+          <t>BDOI's text is met: Request source (Marketing, TSU, Insurer) with the details of BDOI's form and the three-level Marketing approval by setting (TC-FRPM.011.02 cases).</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Adopt BDOI wording – Load Annex F as the slip templates (configuration); keep system e-mail (C12); file naming and slip per insurer as platform changes if confirmed.</t>
+          <t>BDOI's text is met: Package quotation slip per insurer with BDOI's file name, sent from the system (TC-FRPM.012.01 cases).</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Keep rounds and master (PMADD03, 04); decide options per insurer and response values (C14, C15); QS value column is a platform change.</t>
+          <t>BDOI's text is met: Comparative table of the package request with QS value, options per insurer and Final Terms; skipped for the source Insurer (TC-FRPM.012.02 cases).</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Proposal slips per insurer or the package slip (C18).</t>
+          <t>BDOI's text is met: Generate Proposal on the package request: one proposal slip per selected insurer (TC-FRPM.013.01 cases).</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Quorum, President and routing (C17); platform change for parallel then sequential routing.</t>
+          <t>BDOI's text is met: ManCom approvers selected, approving in parallel, then the President (setting) (TC-FRPM.014.01 cases).</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Keep ours – BRPM.015 asks for automatic forwarding; confirm with BDOI (C20).</t>
+          <t>BDOI's text is met: Request for Deployment button or automatic forwarding by setting, with the deployment request number (TC-FRPM.015.01 cases).</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Adopt BDOI wording – Add the notice to the original assignee (small platform change).</t>
+          <t>BDOI's text is met: The original assignee is told when a request is reassigned (TC-FRPM.017.01 cases).</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Needs BDOI decision – Reports builder vs saved variants (C21).; some acceptance criteria partly available</t>
+          <t>BDOI's text is met: Report Builder of Product Maintenance: source, columns, filters and sort, preview, print and export, templates saved and shared (TC-FRPM.020.01 cases).</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Planned extension – Add the action type and reference number filters and the file name.</t>
+          <t>BDOI's text is met: Audit Logs with action type and reference number filters, sortable columns and export named Audit Logs_MMDDYYYY (TC-FRPM.021.01 cases).</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>BDOI's text: Planned extension – Add export of the record history.</t>
+          <t>BDOI's text is met: Audit logs of each record with their export (TC-FRPM.021.02 cases).</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>Added in v1.1; some acceptance criteria partly available</t>
+          <t>Added in v1.1 from the BIBS reference FRS; Part of a reference requirement is not testable yet (conformance register)</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6795,7 @@
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>A deactivation (retirement) request can be returned or voided with its reason; an explicit Reject outcome is point C04.</t>
+          <t>Shown in TC-FRPM.003.07-AC2: the rejected deactivation request shows the approver's remarks and the package stays active.</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>The Expiring tab lists packages within the notice days; the delivered notice is 60 days and is set to 90 at go-live (M.5).</t>
+          <t>Shown in TC-FRPM.004.01-AC1: a package ending in 45 days is in the Expiring tab with 45 days left (notice period 90 days).</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Reports cannot be scheduled yet; the weekly run is planned (programme gap G04).</t>
+          <t>Shown in TC-FRPM.007.01-AC1: the run of Thursday 08:00 lists the quotation requests active or processed in the period with their latest status.</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Report runs are kept in the report archive; the weekly repository comes with the scheduled run.</t>
+          <t>Shown in TC-FRPM.007.01-AC3: the Excel file of the repository has the rows of the preview, in the same order.</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>The Final Terms for Proposal column is not available (comparison: platform status No).</t>
+          <t>Shown in TC-FRPM.009.01-AC1: the Final Terms take the selected insurer's terms; the edited premium is kept in the history.</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="D103" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>Saved report variants are available; sharing a saved definition between users is to be confirmed in UAT.</t>
+          <t>Shown in TC-FRPM.020.01-AC1: a report template saved and shared by the TSU Head gives the TSU Team Lead the same rows.</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="D132" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>Stage notices go to the creator and the assignee; a notice to every TSU Team Lead is not sent.</t>
+          <t>Shown in TC-FRPM.029.01-AC1: the TSU Team Lead is told when a request enters TSU review.</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="D133" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>The change is recorded; its transfer waits for BDOI to name the systems (PQ16).</t>
+          <t>Shown in TC-FRPM.029.01-AC2: the release records the product master change with the product, version and effective date, sent to the receiving systems (simulated in SIT and UAT; connection details from BDOI IT at SIT).</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-03_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-03_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -3129,11 +3129,11 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-070.1-01, TC-PM-070.1-02, TC-PM-070.2-01, TC-PM-070.3-01, TC-PM-070.3-02, TC-PM-073.1-01, TC-PM-073.1-02, TC-PM-073.2-01 ...</t>
+          <t>TC-PM-070.1-01, TC-PM-070.1-02, TC-PM-070.2-01, TC-PM-070.3-01, TC-PM-070.3-02, TC-PM-070.4-01, TC-PM-070.4-02, TC-PM-073.1-01 ...</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -3429,11 +3429,11 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-045.1-01, TC-PM-045.1-02, TC-PM-045.1-03, TC-PM-045.2-01, TC-PM-045.3-01, TC-FRPM.003.04-AC1, TC-FRPM.003.04-AC2</t>
+          <t>TC-PM-045.4-01, TC-PM-045.4-02, TC-PM-045.1-01, TC-PM-045.1-02, TC-PM-045.1-03, TC-PM-045.2-01, TC-PM-045.3-01, TC-PM-SCR-24 ...</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -3529,11 +3529,11 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-024.1-01, TC-PM-024.1-02, TC-PM-024.2-01, TC-PM-024.3-01, TC-PM-024.3-02, TC-PM-024.4-01, TC-PM-045.1-01, TC-PM-045.1-02 ...</t>
+          <t>TC-PM-024.1-01, TC-PM-024.1-02, TC-PM-024.2-01, TC-PM-024.3-01, TC-PM-024.3-02, TC-PM-024.4-01, TC-PM-045.4-01, TC-PM-045.4-02 ...</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -3579,11 +3579,11 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-045.1-01, TC-PM-045.1-02, TC-PM-045.1-03, TC-PM-045.2-01, TC-PM-045.3-01, TC-PM-073.1-01, TC-PM-073.1-02, TC-PM-073.2-01 ...</t>
+          <t>TC-PM-045.4-01, TC-PM-045.4-02, TC-PM-045.1-01, TC-PM-045.1-02, TC-PM-045.1-03, TC-PM-045.2-01, TC-PM-045.3-01, TC-PM-073.1-01 ...</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -3979,11 +3979,11 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-071.1-01, TC-PM-071.2-01, TC-PM-071.2-02, TC-PM-071.3-01, TC-PM-071.3-02, TC-FRPM.007.02-AC1, TC-FRPM.007.02-AC2</t>
+          <t>TC-PM-071.1-01, TC-PM-071.2-01, TC-PM-071.2-02, TC-PM-071.3-01, TC-PM-071.3-02, TC-PM-071.1-02, TC-PM-071.1-03, TC-PM-SCR-26 ...</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -4579,11 +4579,11 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-033.1-01, TC-PM-033.2-01, TC-PM-033.2-02, TC-PM-033.2-03, TC-PM-033.3-01, TC-PM-040.1-01, TC-PM-040.1-02, TC-PM-040.2-01 ...</t>
+          <t>TC-PM-033.4-01, TC-PM-033.4-02, TC-PM-033.4-03, TC-PM-033.1-01, TC-PM-033.2-01, TC-PM-033.2-02, TC-PM-033.2-03, TC-PM-033.3-01 ...</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -4679,11 +4679,11 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-041.1-01, TC-PM-041.1-02, TC-PM-041.2-01, TC-PM-041.3-01, TC-PM-041.4-01, TC-PM-041.4-02, TC-FRPM.014.01-AC1, TC-FRPM.014.01-AC2 ...</t>
+          <t>TC-PM-041.5-01, TC-PM-041.5-02, TC-PM-041.1-01, TC-PM-041.1-02, TC-PM-041.2-01, TC-PM-041.3-01, TC-PM-041.4-01, TC-PM-041.4-02 ...</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -4779,11 +4779,11 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-041.1-01, TC-PM-041.1-02, TC-PM-041.2-01, TC-PM-041.3-01, TC-PM-041.4-01, TC-PM-041.4-02, TC-PM-073.1-01, TC-PM-073.1-02 ...</t>
+          <t>TC-PM-041.5-01, TC-PM-041.5-02, TC-PM-041.1-01, TC-PM-041.1-02, TC-PM-041.2-01, TC-PM-041.3-01, TC-PM-041.4-01, TC-PM-041.4-02 ...</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -5229,11 +5229,11 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-071.1-01, TC-PM-071.2-01, TC-PM-071.2-02, TC-PM-071.3-01, TC-PM-071.3-02, TC-FRPM.020.01-AC1, TC-FRPM.020.01-AC2, TC-FRPM.020.01-AC3</t>
+          <t>TC-PM-071.1-01, TC-PM-071.2-01, TC-PM-071.2-02, TC-PM-071.3-01, TC-PM-071.3-02, TC-PM-071.1-02, TC-PM-071.1-03, TC-PM-SCR-26 ...</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -5279,11 +5279,11 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-005.1-01, TC-PM-005.2-01, TC-PM-005.3-01, TC-FRPM.021.01-AC1, TC-FRPM.021.01-AC2</t>
+          <t>TC-PM-005.4-01, TC-PM-005.1-01, TC-PM-005.2-01, TC-PM-005.3-01, TC-PM-SCR-27, TC-FRPM.021.01-AC1, TC-FRPM.021.01-AC2</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -5329,11 +5329,11 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-005.1-01, TC-PM-005.2-01, TC-PM-005.3-01, TC-FRPM.021.02-AC1</t>
+          <t>TC-PM-005.4-01, TC-PM-005.1-01, TC-PM-005.2-01, TC-PM-005.3-01, TC-PM-SCR-27, TC-FRPM.021.02-AC1</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -5829,11 +5829,11 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-072.1-01, TC-PM-072.1-02, TC-PM-072.2-01, TC-PM-072.1-03, TC-FRPM.029.01-AC1, TC-FRPM.029.01-AC2</t>
+          <t>TC-PM-072.1-01, TC-PM-072.1-02, TC-PM-072.2-01, TC-PM-072.2-02, TC-PM-072.1-03, TC-PM-SCR-25, TC-FRPM.029.01-AC1, TC-FRPM.029.01-AC2</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-03_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-03_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -4288,7 +4288,7 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>WT-A.3, WT-A.4, WT-A.5, WT-A.6, WT-A.12, WT-B.1 ...</t>
+          <t>WT-A.3, WT-A.4, WT-A.5, WT-A.6, WT-A.12, WT-A.14 ...</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>WT-A.7, WT-A.8, WT-A.9, WT-A.10, WT-A.13, WT-A.14 ...</t>
+          <t>WT-A.7, WT-A.8, WT-A.9, WT-A.10, WT-A.13, WT-B.5 ...</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>WT-A.13, WT-A.14, WT-B.8</t>
+          <t>WT-A.13, WT-B.8</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>WT-A.13, WT-A.14, WT-B.8</t>
+          <t>WT-A.13, WT-B.8</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>WT-A.4, WT-A.5, WT-A.6, WT-A.12, WT-A.15, WT-A.16 ...</t>
+          <t>WT-A.4, WT-A.5, WT-A.6, WT-A.12, WT-A.14, WT-A.15 ...</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>WT-A.15, WT-A.16, WT-A.17, WT-A.20, WT-B.9, WT-B.10 ...</t>
+          <t>WT-A.14, WT-A.15, WT-A.16, WT-A.17, WT-A.20, WT-B.9 ...</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-03_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-03_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -696,7 +696,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-03 Product Maintenance – FRS v1.2 in BDOI's template</t>
+          <t>BRD-03 Product Maintenance – FRS v1.3 in BDOI's template</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Availability of every acceptance criterion of the FRS v1.2</t>
+          <t>Availability of every acceptance criterion of the FRS v1.3</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
@@ -5959,7 +5959,7 @@
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Availability of every acceptance criterion of the FRS v1.2</t>
+          <t>Availability of every acceptance criterion of the FRS v1.3</t>
         </is>
       </c>
     </row>
